--- a/assets/demo/northstar-pilot-economics.xlsx
+++ b/assets/demo/northstar-pilot-economics.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pilot economics" sheetId="1" r:id="Rbbdacef21e48419b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pilot economics" sheetId="1" r:id="R8159313f7e284036"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -448,7 +448,7 @@
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="13" t="str">
-        <x:v>Monthly contribution</x:v>
+        <x:v>Operating surplus</x:v>
       </x:c>
       <x:c r="B12" s="14" t="n">
         <x:f>B8-B10-B11</x:f>
@@ -464,7 +464,7 @@
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
       <x:c r="A13" s="13" t="str">
-        <x:v>Contribution margin</x:v>
+        <x:v>Surplus margin</x:v>
       </x:c>
       <x:c r="B13" s="15" t="n">
         <x:f>B12/B8</x:f>
